--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.44414621986316</v>
+        <v>3.809673760727764</v>
       </c>
       <c r="D2" t="n">
-        <v>23.10977647972958</v>
+        <v>3.755338677956056</v>
       </c>
       <c r="E2" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F2" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.21643525555881</v>
+        <v>7.347670729028306</v>
       </c>
       <c r="D3" t="n">
-        <v>45.36253459323959</v>
+        <v>7.371411871401435</v>
       </c>
       <c r="E3" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F3" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.88959708544269</v>
+        <v>6.319559526384437</v>
       </c>
       <c r="D4" t="n">
-        <v>38.7707361395088</v>
+        <v>6.30024462267018</v>
       </c>
       <c r="E4" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F4" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.65564173119777</v>
+        <v>5.144041781319638</v>
       </c>
       <c r="D5" t="n">
-        <v>31.45444743676192</v>
+        <v>5.111347708473812</v>
       </c>
       <c r="E5" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F5" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.95785093996933</v>
+        <v>5.518150777745017</v>
       </c>
       <c r="D6" t="n">
-        <v>34.25501212928658</v>
+        <v>5.56643947100907</v>
       </c>
       <c r="E6" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F6" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.22659604765641</v>
+        <v>4.586821857744166</v>
       </c>
       <c r="D7" t="n">
-        <v>28.51808630312031</v>
+        <v>4.634189024257051</v>
       </c>
       <c r="E7" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F7" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.80087395157104</v>
+        <v>5.655142017130294</v>
       </c>
       <c r="D8" t="n">
-        <v>34.81417017179174</v>
+        <v>5.657302652916157</v>
       </c>
       <c r="E8" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F8" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.16436997484592</v>
+        <v>4.089210120912463</v>
       </c>
       <c r="D9" t="n">
-        <v>25.48274433006405</v>
+        <v>4.140945953635408</v>
       </c>
       <c r="E9" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F9" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.60573409276882</v>
+        <v>6.435931790074934</v>
       </c>
       <c r="D10" t="n">
-        <v>39.58570887107773</v>
+        <v>6.432677691550132</v>
       </c>
       <c r="E10" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F10" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>81.32469131085544</v>
+        <v>13.21526233801401</v>
       </c>
       <c r="D11" t="n">
-        <v>44.38480439807595</v>
+        <v>7.212530714687342</v>
       </c>
       <c r="E11" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F11" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>79.78884343796247</v>
+        <v>12.9656870586689</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3841476857205369</v>
+        <v>0.06242399892958726</v>
       </c>
       <c r="E12" t="n">
-        <v>19.16709829518287</v>
+        <v>3.114653472967216</v>
       </c>
       <c r="F12" t="n">
-        <v>11.97984878362211</v>
+        <v>1.946725427338593</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
